--- a/sheets/민요/검수/제목없음 (이미지 (28)).xlsx
+++ b/sheets/민요/검수/제목없음 (이미지 (28)).xlsx
@@ -4,14 +4,14 @@
   <sheets>
     <sheet name="정보" sheetId="1" r:id="rId1"/>
     <sheet name="정간목록" sheetId="2" r:id="rId2"/>
-    <sheet name="악보 1" sheetId="3" r:id="rId3"/>
+    <sheet name="악보" sheetId="3" r:id="rId3"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <name val="맑은 고딕"/>
@@ -20,6 +20,26 @@
     <font>
       <b/>
       <sz val="11"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="맑은 고딕"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="맑은 고딕"/>
+    </font>
+    <font>
+      <sz val="22"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="13"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
     </font>
@@ -50,7 +70,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -73,11 +93,71 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFFFFFFF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFFFFFFF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFFFFFFF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFFFFFFF"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -96,6 +176,54 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -907,202 +1035,197 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <pageSetUpPr fitToPage="0"/>
+  </sheetPr>
+  <dimension ref="A1:C14"/>
   <cols>
-    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="1" max="1" width="2" customWidth="1"/>
     <col min="2" max="2" width="9" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">제목없음 (이미지 (28)) — 민요채보-1/이미지 (28).png</t>
-        </is>
-      </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">정간</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1줄</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="1">
-        <v>1</v>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
+    <row r="1"/>
+    <row r="2" ht="60" customHeight="1">
+      <c s="8" t="inlineStr" r="B2">
+        <is>
+          <t xml:space="preserve">제목없음 (이미지 (28))</t>
+        </is>
+      </c>
+      <c s="8" r="C2"/>
+    </row>
+    <row r="3" ht="56" customHeight="1">
+      <c r="B3" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">淋淋</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">간</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="1">
-        <v>2</v>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="C4" s="2"/>
-    </row>
-    <row r="5" ht="32" customHeight="1">
-      <c r="A5" s="1">
-        <v>3</v>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+    <row r="4" ht="56" customHeight="1">
+      <c r="B4" s="15" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="C4" s="18"/>
+    </row>
+    <row r="5" ht="56" customHeight="1">
+      <c r="B5" s="15" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 △</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="C5" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">다</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="1">
-        <v>4</v>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
+    <row r="6" ht="56" customHeight="1">
+      <c r="B6" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">汰仲</t>
         </is>
       </c>
-      <c r="C6" s="3"/>
-    </row>
-    <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="1">
-        <v>5</v>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="C7" s="2"/>
-    </row>
-    <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="1">
-        <v>6</v>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="C6" s="20"/>
+    </row>
+    <row r="7" ht="56" customHeight="1">
+      <c r="B7" s="15" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="C7" s="18"/>
+    </row>
+    <row r="8" ht="56" customHeight="1">
+      <c r="B8" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">간</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="32" customHeight="1">
-      <c r="A9" s="1">
-        <v>7</v>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
+    <row r="9" ht="56" customHeight="1">
+      <c r="B9" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">△
 姑太</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">령</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="1">
-        <v>8</v>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
+    <row r="10" ht="56" customHeight="1">
+      <c r="B10" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">姑太</t>
         </is>
       </c>
-      <c r="C10" s="3"/>
-    </row>
-    <row r="11" ht="32" customHeight="1">
-      <c r="A11" s="1">
-        <v>9</v>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+      <c r="C10" s="22"/>
+    </row>
+    <row r="11" ht="56" customHeight="1">
+      <c r="B11" s="15" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 △</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="C11" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">님이</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="1">
-        <v>10</v>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
+    <row r="12" ht="56" customHeight="1">
+      <c r="B12" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="C12" s="2"/>
-    </row>
-    <row r="13" ht="32" customHeight="1">
-      <c r="A13" s="1">
-        <v>11</v>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="C12" s="17"/>
+    </row>
+    <row r="13" ht="56" customHeight="1">
+      <c r="B13" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">△
 黃太</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C13" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">떠나</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="1">
-        <v>12</v>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
+    <row r="14" ht="56" customHeight="1">
+      <c r="B14" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">黃無</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">간다</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B2:C2"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" fitToWidth="1" fitToHeight="0" scale="100"/>
 </worksheet>
 </file>
--- a/sheets/민요/검수/제목없음 (이미지 (28)).xlsx
+++ b/sheets/민요/검수/제목없음 (이미지 (28)).xlsx
@@ -361,7 +361,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">제목 없는 손채보 조각. 손으로 그린 12정간 격자(번호 없음), 굵은 선 3칸마다 → 3/4·12. 거의 빈 용지로, 오른쪽에서 두 줄에만 내용이 있음(그 오른쪽 끝 열은 비어 있어 율명 줄 1부터 셈). 줄2는 율명 없이 짧은 사선(ﾉ)·세로 획(―)과 세모만 있음(기호표 밖 획은 ﾉ·―로 적음). 가사: 깐다 깐다 정든 님이 떠나간다.</t>
+          <t xml:space="preserve">제목 없는 손채보 조각. 손으로 그린 12정간 격자(번호 없음), 굵은 선 3칸마다 → 3/4·12. 거의 빈 용지로, 오른쪽에서 두 줄에만 내용이 있음(그 오른쪽 끝 열은 비어 있어 율명 줄 1부터 셈). 줄2는 율명 없이 짧은 사선(ﾉ)·세로 획(–)과 세모만 있음(기호표 밖 획은 ﾉ·–로 적음). 가사: 깐다 깐다 정든 님이 떠나간다.</t>
         </is>
       </c>
     </row>
@@ -409,7 +409,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">― 연음 · △ 쉼 · 점 · ○ 동그라미 · ⁚ 두 점 · ‹ 정간 경계 표시 · ／ 사선 (· ○ ⁚ ‹ ／ 는 화면 표시 전용)</t>
+          <t xml:space="preserve">– 연음 · △ 쉼 · 점 · ○ 동그라미 · ⁚ 두 점 · ‹ 정간 경계 표시 · ／ 사선 (· ○ ⁚ ‹ ／ 는 화면 표시 전용)</t>
         </is>
       </c>
     </row>
@@ -631,12 +631,12 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|△</t>
+          <t xml:space="preserve">–|△</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 △</t>
         </is>
       </c>
@@ -667,13 +667,13 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">林仲|―</t>
+          <t xml:space="preserve">林仲|–</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">林仲
-―</t>
+–</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -826,12 +826,12 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|△</t>
+          <t xml:space="preserve">–|△</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 △</t>
         </is>
       </c>
@@ -1051,12 +1051,12 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I15" s="2"/>
@@ -1156,12 +1156,12 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|△</t>
+          <t xml:space="preserve">–|△</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 △</t>
         </is>
       </c>
@@ -1240,13 +1240,13 @@
       <c r="A5" s="0"/>
       <c r="B5" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="C5" s="10"/>
       <c r="D5" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 △</t>
         </is>
       </c>
@@ -1263,7 +1263,7 @@
       <c r="D6" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">林仲
-―</t>
+–</t>
         </is>
       </c>
       <c r="E6" s="8" t="inlineStr">
@@ -1295,7 +1295,7 @@
       <c r="A8" s="0"/>
       <c r="B8" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 △</t>
         </is>
       </c>
@@ -1341,7 +1341,7 @@
       <c r="C11" s="10"/>
       <c r="D11" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 △</t>
         </is>
       </c>

--- a/sheets/민요/검수/제목없음 (이미지 (28)).xlsx
+++ b/sheets/민요/검수/제목없음 (이미지 (28)).xlsx
@@ -11,27 +11,43 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="4">
+  <fonts count="7">
     <font>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="22"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="24"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="24"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -134,7 +150,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -157,7 +173,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <!-- 8~16: 박 묶음 가사 칸 = (일반 8~10 · 비고 11~13 · 팔레트 외 14~16) × (첫 · 가운데 · 마지막) -->
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -185,7 +200,6 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <!-- 17~19: 악보 율명 칸 22pt (가사 11pt 의 두 배) = 일반 · 비고 · 팔레트 외 -->
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -193,6 +207,30 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1189,29 +1227,29 @@
     </row>
     <row r="2" ht="60" customHeight="1">
       <c r="A2" s="0"/>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">제목없음 (이미지 (28))</t>
         </is>
       </c>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
     </row>
     <row r="3" ht="56" customHeight="1">
       <c r="A3" s="0"/>
-      <c r="B3" s="17" t="inlineStr">
+      <c r="B3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">ﾉ</t>
         </is>
       </c>
-      <c r="C3" s="8"/>
-      <c r="D3" s="18" t="inlineStr">
+      <c r="C3" s="22"/>
+      <c r="D3" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">林</t>
         </is>
       </c>
-      <c r="E3" s="11" t="inlineStr">
+      <c r="E3" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">깐</t>
         </is>
@@ -1219,18 +1257,18 @@
     </row>
     <row r="4" ht="56" customHeight="1">
       <c r="A4" s="0"/>
-      <c r="B4" s="17" t="inlineStr">
+      <c r="B4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">ﾉ</t>
         </is>
       </c>
-      <c r="C4" s="9"/>
-      <c r="D4" s="17" t="inlineStr">
+      <c r="C4" s="25"/>
+      <c r="D4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">林</t>
         </is>
       </c>
-      <c r="E4" s="9" t="inlineStr">
+      <c r="E4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">다</t>
         </is>
@@ -1238,35 +1276,35 @@
     </row>
     <row r="5" ht="56" customHeight="1">
       <c r="A5" s="0"/>
-      <c r="B5" s="17" t="inlineStr">
+      <c r="B5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C5" s="10"/>
-      <c r="D5" s="17" t="inlineStr">
+      <c r="C5" s="26"/>
+      <c r="D5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 △</t>
         </is>
       </c>
-      <c r="E5" s="10"/>
+      <c r="E5" s="26"/>
     </row>
     <row r="6" ht="56" customHeight="1">
       <c r="A6" s="0"/>
-      <c r="B6" s="17" t="inlineStr">
+      <c r="B6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">ﾉ</t>
         </is>
       </c>
-      <c r="C6" s="8"/>
-      <c r="D6" s="17" t="inlineStr">
+      <c r="C6" s="22"/>
+      <c r="D6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">林仲
 –</t>
         </is>
       </c>
-      <c r="E6" s="8" t="inlineStr">
+      <c r="E6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">깐</t>
         </is>
@@ -1274,18 +1312,18 @@
     </row>
     <row r="7" ht="56" customHeight="1">
       <c r="A7" s="0"/>
-      <c r="B7" s="17" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">ﾉ</t>
         </is>
       </c>
-      <c r="C7" s="9"/>
-      <c r="D7" s="17" t="inlineStr">
+      <c r="C7" s="25"/>
+      <c r="D7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="E7" s="9" t="inlineStr">
+      <c r="E7" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">다</t>
         </is>
@@ -1293,27 +1331,27 @@
     </row>
     <row r="8" ht="56" customHeight="1">
       <c r="A8" s="0"/>
-      <c r="B8" s="17" t="inlineStr">
+      <c r="B8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 △</t>
         </is>
       </c>
-      <c r="C8" s="10"/>
-      <c r="D8" s="17"/>
-      <c r="E8" s="10"/>
+      <c r="C8" s="26"/>
+      <c r="D8" s="21"/>
+      <c r="E8" s="26"/>
     </row>
     <row r="9" ht="56" customHeight="1">
       <c r="A9" s="0"/>
-      <c r="B9" s="17"/>
-      <c r="C9" s="8"/>
-      <c r="D9" s="17" t="inlineStr">
+      <c r="B9" s="21"/>
+      <c r="C9" s="22"/>
+      <c r="D9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△
 姑太</t>
         </is>
       </c>
-      <c r="E9" s="8" t="inlineStr">
+      <c r="E9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">정든</t>
         </is>
@@ -1321,15 +1359,15 @@
     </row>
     <row r="10" ht="56" customHeight="1">
       <c r="A10" s="0"/>
-      <c r="B10" s="17"/>
-      <c r="C10" s="9"/>
-      <c r="D10" s="17" t="inlineStr">
+      <c r="B10" s="21"/>
+      <c r="C10" s="25"/>
+      <c r="D10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 姑</t>
         </is>
       </c>
-      <c r="E10" s="9" t="inlineStr">
+      <c r="E10" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">님이</t>
         </is>
@@ -1337,38 +1375,38 @@
     </row>
     <row r="11" ht="56" customHeight="1">
       <c r="A11" s="0"/>
-      <c r="B11" s="17"/>
-      <c r="C11" s="10"/>
-      <c r="D11" s="17" t="inlineStr">
+      <c r="B11" s="21"/>
+      <c r="C11" s="26"/>
+      <c r="D11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 △</t>
         </is>
       </c>
-      <c r="E11" s="10"/>
+      <c r="E11" s="26"/>
     </row>
     <row r="12" ht="56" customHeight="1">
       <c r="A12" s="0"/>
-      <c r="B12" s="17"/>
-      <c r="C12" s="8"/>
-      <c r="D12" s="17" t="inlineStr">
+      <c r="B12" s="21"/>
+      <c r="C12" s="22"/>
+      <c r="D12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="E12" s="8"/>
+      <c r="E12" s="22"/>
     </row>
     <row r="13" ht="56" customHeight="1">
       <c r="A13" s="0"/>
-      <c r="B13" s="17"/>
-      <c r="C13" s="9"/>
-      <c r="D13" s="17" t="inlineStr">
+      <c r="B13" s="21"/>
+      <c r="C13" s="25"/>
+      <c r="D13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△
 黃黃</t>
         </is>
       </c>
-      <c r="E13" s="9" t="inlineStr">
+      <c r="E13" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">떠나</t>
         </is>
@@ -1376,15 +1414,15 @@
     </row>
     <row r="14" ht="56" customHeight="1">
       <c r="A14" s="0"/>
-      <c r="B14" s="17"/>
-      <c r="C14" s="10"/>
-      <c r="D14" s="18" t="inlineStr">
+      <c r="B14" s="21"/>
+      <c r="C14" s="26"/>
+      <c r="D14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">太黃
 㑲</t>
         </is>
       </c>
-      <c r="E14" s="13" t="inlineStr">
+      <c r="E14" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">간다</t>
         </is>

--- a/sheets/민요/검수/제목없음 (이미지 (28)).xlsx
+++ b/sheets/민요/검수/제목없음 (이미지 (28)).xlsx
@@ -1216,16 +1216,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="55.19" customHeight="1">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -1236,7 +1236,7 @@
       <c r="D2" s="20"/>
       <c r="E2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="55.19" customHeight="1">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -1255,7 +1255,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="55.19" customHeight="1">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="55.19" customHeight="1">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
       </c>
       <c r="E5" s="26"/>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="55.19" customHeight="1">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="55.19" customHeight="1">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -1329,7 +1329,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="55.19" customHeight="1">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -1341,7 +1341,7 @@
       <c r="D8" s="21"/>
       <c r="E8" s="26"/>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="55.19" customHeight="1">
       <c r="A9" s="0"/>
       <c r="B9" s="21"/>
       <c r="C9" s="22"/>
@@ -1357,7 +1357,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="55.19" customHeight="1">
       <c r="A10" s="0"/>
       <c r="B10" s="21"/>
       <c r="C10" s="25"/>
@@ -1373,7 +1373,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="55.19" customHeight="1">
       <c r="A11" s="0"/>
       <c r="B11" s="21"/>
       <c r="C11" s="26"/>
@@ -1385,18 +1385,18 @@
       </c>
       <c r="E11" s="26"/>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="55.19" customHeight="1">
       <c r="A12" s="0"/>
       <c r="B12" s="21"/>
       <c r="C12" s="22"/>
       <c r="D12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="E12" s="22"/>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="55.19" customHeight="1">
       <c r="A13" s="0"/>
       <c r="B13" s="21"/>
       <c r="C13" s="25"/>
@@ -1412,7 +1412,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="55.19" customHeight="1">
       <c r="A14" s="0"/>
       <c r="B14" s="21"/>
       <c r="C14" s="26"/>

--- a/sheets/민요/검수/제목없음 (이미지 (28)).xlsx
+++ b/sheets/민요/검수/제목없음 (이미지 (28)).xlsx
@@ -1353,7 +1353,8 @@
       </c>
       <c r="E9" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">정든</t>
+          <t xml:space="preserve">정
+든</t>
         </is>
       </c>
     </row>
@@ -1369,7 +1370,8 @@
       </c>
       <c r="E10" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">님이</t>
+          <t xml:space="preserve">님
+이</t>
         </is>
       </c>
     </row>
@@ -1408,7 +1410,8 @@
       </c>
       <c r="E13" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">떠나</t>
+          <t xml:space="preserve">떠
+나</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1427,8 @@
       </c>
       <c r="E14" s="27" t="inlineStr">
         <is>
-          <t xml:space="preserve">간다</t>
+          <t xml:space="preserve">간
+다</t>
         </is>
       </c>
     </row>

--- a/sheets/민요/검수/제목없음 (이미지 (28)).xlsx
+++ b/sheets/민요/검수/제목없음 (이미지 (28)).xlsx
@@ -11,7 +11,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <name val="궁서체"/>
@@ -47,6 +47,11 @@
     </font>
     <font>
       <sz val="12"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="18"/>
       <name val="궁서체"/>
       <family val="2"/>
     </font>
@@ -150,7 +155,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -231,6 +236,21 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1243,13 +1263,13 @@
           <t xml:space="preserve">ﾉ</t>
         </is>
       </c>
-      <c r="C3" s="22"/>
+      <c r="C3" s="28"/>
       <c r="D3" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">林</t>
         </is>
       </c>
-      <c r="E3" s="24" t="inlineStr">
+      <c r="E3" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">깐</t>
         </is>
@@ -1262,13 +1282,13 @@
           <t xml:space="preserve">ﾉ</t>
         </is>
       </c>
-      <c r="C4" s="25"/>
+      <c r="C4" s="30"/>
       <c r="D4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">林</t>
         </is>
       </c>
-      <c r="E4" s="25" t="inlineStr">
+      <c r="E4" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">다</t>
         </is>
@@ -1281,14 +1301,14 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C5" s="26"/>
+      <c r="C5" s="31"/>
       <c r="D5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 △</t>
         </is>
       </c>
-      <c r="E5" s="26"/>
+      <c r="E5" s="31"/>
     </row>
     <row r="6" ht="55.19" customHeight="1">
       <c r="A6" s="0"/>
@@ -1297,14 +1317,14 @@
           <t xml:space="preserve">ﾉ</t>
         </is>
       </c>
-      <c r="C6" s="22"/>
+      <c r="C6" s="28"/>
       <c r="D6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">林仲
 –</t>
         </is>
       </c>
-      <c r="E6" s="22" t="inlineStr">
+      <c r="E6" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">깐</t>
         </is>
@@ -1317,13 +1337,13 @@
           <t xml:space="preserve">ﾉ</t>
         </is>
       </c>
-      <c r="C7" s="25"/>
+      <c r="C7" s="30"/>
       <c r="D7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="E7" s="25" t="inlineStr">
+      <c r="E7" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">다</t>
         </is>
@@ -1337,21 +1357,21 @@
 △</t>
         </is>
       </c>
-      <c r="C8" s="26"/>
+      <c r="C8" s="31"/>
       <c r="D8" s="21"/>
-      <c r="E8" s="26"/>
+      <c r="E8" s="31"/>
     </row>
     <row r="9" ht="55.19" customHeight="1">
       <c r="A9" s="0"/>
       <c r="B9" s="21"/>
-      <c r="C9" s="22"/>
+      <c r="C9" s="28"/>
       <c r="D9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△
 姑太</t>
         </is>
       </c>
-      <c r="E9" s="22" t="inlineStr">
+      <c r="E9" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">정
 든</t>
@@ -1361,14 +1381,14 @@
     <row r="10" ht="55.19" customHeight="1">
       <c r="A10" s="0"/>
       <c r="B10" s="21"/>
-      <c r="C10" s="25"/>
+      <c r="C10" s="30"/>
       <c r="D10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 姑</t>
         </is>
       </c>
-      <c r="E10" s="25" t="inlineStr">
+      <c r="E10" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">님
 이</t>
@@ -1378,37 +1398,37 @@
     <row r="11" ht="55.19" customHeight="1">
       <c r="A11" s="0"/>
       <c r="B11" s="21"/>
-      <c r="C11" s="26"/>
+      <c r="C11" s="31"/>
       <c r="D11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 △</t>
         </is>
       </c>
-      <c r="E11" s="26"/>
+      <c r="E11" s="31"/>
     </row>
     <row r="12" ht="55.19" customHeight="1">
       <c r="A12" s="0"/>
       <c r="B12" s="21"/>
-      <c r="C12" s="22"/>
+      <c r="C12" s="28"/>
       <c r="D12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E12" s="22"/>
+      <c r="E12" s="28"/>
     </row>
     <row r="13" ht="55.19" customHeight="1">
       <c r="A13" s="0"/>
       <c r="B13" s="21"/>
-      <c r="C13" s="25"/>
+      <c r="C13" s="30"/>
       <c r="D13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△
 黃黃</t>
         </is>
       </c>
-      <c r="E13" s="25" t="inlineStr">
+      <c r="E13" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">떠
 나</t>
@@ -1418,14 +1438,14 @@
     <row r="14" ht="55.19" customHeight="1">
       <c r="A14" s="0"/>
       <c r="B14" s="21"/>
-      <c r="C14" s="26"/>
+      <c r="C14" s="31"/>
       <c r="D14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">太黃
 㑲</t>
         </is>
       </c>
-      <c r="E14" s="27" t="inlineStr">
+      <c r="E14" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">간
 다</t>

--- a/sheets/민요/검수/제목없음 (이미지 (28)).xlsx
+++ b/sheets/민요/검수/제목없음 (이미지 (28)).xlsx
@@ -11,7 +11,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="8">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <name val="궁서체"/>
@@ -42,11 +42,6 @@
     </font>
     <font>
       <sz val="24"/>
-      <name val="궁서체"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="12"/>
       <name val="궁서체"/>
       <family val="2"/>
     </font>
@@ -155,7 +150,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -217,40 +212,28 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -355,7 +338,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
     </row>
@@ -379,7 +362,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">상</t>
+          <t xml:space="preserve">하</t>
         </is>
       </c>
     </row>
@@ -391,7 +374,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">제목 없음</t>
+          <t xml:space="preserve">비고 53%, 제목 없음</t>
         </is>
       </c>
     </row>
@@ -419,7 +402,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">제목 없는 손채보 조각. 손으로 그린 12정간 격자(번호 없음), 굵은 선 3칸마다 → 3/4·12. 거의 빈 용지로, 오른쪽에서 두 줄에만 내용이 있음(그 오른쪽 끝 열은 비어 있어 율명 줄 1부터 셈). 줄2는 율명 없이 짧은 사선(ﾉ)·세로 획(–)과 세모만 있음(기호표 밖 획은 ﾉ·–로 적음). 가사: 깐다 깐다 정든 님이 떠나간다.</t>
+          <t xml:space="preserve">10-13 전면 재판독. 제목 없는 손채보, 손으로 그린 격자(번호 없음), 12정간·굵은 선 3칸마다 → 3/4·12. 오른쪽 끝 열은 비어 있어 그 왼쪽 율명 열을 줄1로 셈. 내용은 2줄뿐(나머지 왼쪽 줄은 빈 칸). 줄2는 율명 없이 세로·사선 획과 세모만 있음(장구 등 반주 표시로 보임) — 기호표에 없어 모두 ﾉ 로 적고 비고에 모양. 가사: 깐다 깐다 정든 님이 떠나간다.</t>
         </is>
       </c>
     </row>
@@ -622,7 +605,7 @@
       </c>
       <c r="J2" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">왼쪽에 굵은 세로획 하나 더 있음 — 㑣(亻林) 가능성</t>
+          <t xml:space="preserve">왼쪽에 굵은 세로획 덧씀 — 㑣(亻林) 가능성</t>
         </is>
       </c>
       <c r="K2" s="2"/>
@@ -648,22 +631,26 @@
       <c r="F3" s="2">
         <v>1</v>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">林</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">林</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">다</t>
         </is>
       </c>
-      <c r="J3" s="4"/>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">왼쪽에 亻 같은 획 겹침 — 㑣 가능성</t>
+        </is>
+      </c>
       <c r="K3" s="2"/>
     </row>
     <row r="4">
@@ -995,13 +982,13 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">太黃|㑲</t>
+          <t xml:space="preserve">太黃|㑣</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">太黃
-㑲</t>
+㑣</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
@@ -1011,7 +998,7 @@
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">㑲: 亻+冂 안 十 모양(南 흘림), 僙 가능성</t>
+          <t xml:space="preserve">亻+林 모양, 㑲 가능성</t>
         </is>
       </c>
       <c r="K12" s="2"/>
@@ -1037,18 +1024,22 @@
       <c r="F13" s="2">
         <v>1</v>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="G13" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">ﾉ</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="H13" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">ﾉ</t>
         </is>
       </c>
-      <c r="I13" s="2"/>
-      <c r="J13" s="4"/>
+      <c r="I13" s="3"/>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">오른쪽으로 휜 세로 획 )</t>
+        </is>
+      </c>
       <c r="K13" s="2"/>
     </row>
     <row r="14">
@@ -1072,18 +1063,22 @@
       <c r="F14" s="2">
         <v>1</v>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G14" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">ﾉ</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="H14" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">ﾉ</t>
         </is>
       </c>
-      <c r="I14" s="2"/>
-      <c r="J14" s="4"/>
+      <c r="I14" s="3"/>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">사선 획 丿</t>
+        </is>
+      </c>
       <c r="K14" s="2"/>
     </row>
     <row r="15">
@@ -1107,18 +1102,22 @@
       <c r="F15" s="2">
         <v>1</v>
       </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="I15" s="2"/>
-      <c r="J15" s="4"/>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ﾉ</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ﾉ</t>
+        </is>
+      </c>
+      <c r="I15" s="3"/>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">곧은 세로 획 |</t>
+        </is>
+      </c>
       <c r="K15" s="2"/>
     </row>
     <row r="16">
@@ -1142,18 +1141,22 @@
       <c r="F16" s="2">
         <v>2</v>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="G16" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">ﾉ</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="H16" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">ﾉ</t>
         </is>
       </c>
-      <c r="I16" s="2"/>
-      <c r="J16" s="4"/>
+      <c r="I16" s="3"/>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">짧은 사선 획 \</t>
+        </is>
+      </c>
       <c r="K16" s="2"/>
     </row>
     <row r="17">
@@ -1177,18 +1180,22 @@
       <c r="F17" s="2">
         <v>2</v>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="G17" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">ﾉ</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="H17" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">ﾉ</t>
         </is>
       </c>
-      <c r="I17" s="2"/>
-      <c r="J17" s="4"/>
+      <c r="I17" s="3"/>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">짧은 사선 획 \</t>
+        </is>
+      </c>
       <c r="K17" s="2"/>
     </row>
     <row r="18">
@@ -1212,19 +1219,23 @@
       <c r="F18" s="2">
         <v>2</v>
       </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–|△</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ﾉ|△</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ﾉ
 △</t>
         </is>
       </c>
-      <c r="I18" s="2"/>
-      <c r="J18" s="4"/>
+      <c r="I18" s="3"/>
+      <c r="J18" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">세로 획 | 다음 세모</t>
+        </is>
+      </c>
       <c r="K18" s="2"/>
     </row>
   </sheetData>
@@ -1245,7 +1256,7 @@
     <row r="1">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="55.19" customHeight="1">
+    <row r="2" ht="52.21" customHeight="1">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -1256,196 +1267,196 @@
       <c r="D2" s="20"/>
       <c r="E2" s="20"/>
     </row>
-    <row r="3" ht="55.19" customHeight="1">
+    <row r="3" ht="52.21" customHeight="1">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">ﾉ</t>
         </is>
       </c>
-      <c r="C3" s="28"/>
-      <c r="D3" s="23" t="inlineStr">
+      <c r="C3" s="22"/>
+      <c r="D3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">林</t>
         </is>
       </c>
-      <c r="E3" s="29" t="inlineStr">
+      <c r="E3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">깐</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="55.19" customHeight="1">
+    <row r="4" ht="52.21" customHeight="1">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">ﾉ</t>
         </is>
       </c>
-      <c r="C4" s="30"/>
+      <c r="C4" s="23"/>
       <c r="D4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">林</t>
         </is>
       </c>
-      <c r="E4" s="30" t="inlineStr">
+      <c r="E4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">다</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="55.19" customHeight="1">
+    <row r="5" ht="52.21" customHeight="1">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="C5" s="31"/>
-      <c r="D5" s="21" t="inlineStr">
+          <t xml:space="preserve">ﾉ</t>
+        </is>
+      </c>
+      <c r="C5" s="24"/>
+      <c r="D5" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 △</t>
         </is>
       </c>
-      <c r="E5" s="31"/>
-    </row>
-    <row r="6" ht="55.19" customHeight="1">
+      <c r="E5" s="26"/>
+    </row>
+    <row r="6" ht="52.21" customHeight="1">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">ﾉ</t>
         </is>
       </c>
-      <c r="C6" s="28"/>
-      <c r="D6" s="21" t="inlineStr">
+      <c r="C6" s="22"/>
+      <c r="D6" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">林仲
 –</t>
         </is>
       </c>
-      <c r="E6" s="28" t="inlineStr">
+      <c r="E6" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">깐</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="55.19" customHeight="1">
+    <row r="7" ht="52.21" customHeight="1">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">ﾉ</t>
         </is>
       </c>
-      <c r="C7" s="30"/>
-      <c r="D7" s="21" t="inlineStr">
+      <c r="C7" s="23"/>
+      <c r="D7" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="E7" s="30" t="inlineStr">
+      <c r="E7" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">다</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="55.19" customHeight="1">
+    <row r="8" ht="52.21" customHeight="1">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
+          <t xml:space="preserve">ﾉ
+△</t>
+        </is>
+      </c>
+      <c r="C8" s="24"/>
+      <c r="D8" s="25"/>
+      <c r="E8" s="26"/>
+    </row>
+    <row r="9" ht="52.21" customHeight="1">
+      <c r="A9" s="0"/>
+      <c r="B9" s="25"/>
+      <c r="C9" s="27"/>
+      <c r="D9" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">△
+姑太</t>
+        </is>
+      </c>
+      <c r="E9" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">정
+든</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="52.21" customHeight="1">
+      <c r="A10" s="0"/>
+      <c r="B10" s="25"/>
+      <c r="C10" s="28"/>
+      <c r="D10" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑
+姑</t>
+        </is>
+      </c>
+      <c r="E10" s="28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">님
+이</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="52.21" customHeight="1">
+      <c r="A11" s="0"/>
+      <c r="B11" s="25"/>
+      <c r="C11" s="26"/>
+      <c r="D11" s="25" t="inlineStr">
+        <is>
           <t xml:space="preserve">–
 △</t>
         </is>
       </c>
-      <c r="C8" s="31"/>
-      <c r="D8" s="21"/>
-      <c r="E8" s="31"/>
-    </row>
-    <row r="9" ht="55.19" customHeight="1">
-      <c r="A9" s="0"/>
-      <c r="B9" s="21"/>
-      <c r="C9" s="28"/>
-      <c r="D9" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">△
-姑太</t>
-        </is>
-      </c>
-      <c r="E9" s="28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">정
-든</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="55.19" customHeight="1">
-      <c r="A10" s="0"/>
-      <c r="B10" s="21"/>
-      <c r="C10" s="30"/>
-      <c r="D10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑
-姑</t>
-        </is>
-      </c>
-      <c r="E10" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">님
-이</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="55.19" customHeight="1">
-      <c r="A11" s="0"/>
-      <c r="B11" s="21"/>
-      <c r="C11" s="31"/>
-      <c r="D11" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–
-△</t>
-        </is>
-      </c>
-      <c r="E11" s="31"/>
-    </row>
-    <row r="12" ht="55.19" customHeight="1">
+      <c r="E11" s="26"/>
+    </row>
+    <row r="12" ht="52.21" customHeight="1">
       <c r="A12" s="0"/>
-      <c r="B12" s="21"/>
-      <c r="C12" s="28"/>
-      <c r="D12" s="21" t="inlineStr">
+      <c r="B12" s="25"/>
+      <c r="C12" s="27"/>
+      <c r="D12" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E12" s="28"/>
-    </row>
-    <row r="13" ht="55.19" customHeight="1">
+      <c r="E12" s="27"/>
+    </row>
+    <row r="13" ht="52.21" customHeight="1">
       <c r="A13" s="0"/>
-      <c r="B13" s="21"/>
-      <c r="C13" s="30"/>
-      <c r="D13" s="21" t="inlineStr">
+      <c r="B13" s="25"/>
+      <c r="C13" s="28"/>
+      <c r="D13" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">△
 黃黃</t>
         </is>
       </c>
-      <c r="E13" s="30" t="inlineStr">
+      <c r="E13" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">떠
 나</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="55.19" customHeight="1">
+    <row r="14" ht="52.21" customHeight="1">
       <c r="A14" s="0"/>
-      <c r="B14" s="21"/>
-      <c r="C14" s="31"/>
-      <c r="D14" s="23" t="inlineStr">
+      <c r="B14" s="25"/>
+      <c r="C14" s="26"/>
+      <c r="D14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">太黃
-㑲</t>
-        </is>
-      </c>
-      <c r="E14" s="32" t="inlineStr">
+㑣</t>
+        </is>
+      </c>
+      <c r="E14" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">간
 다</t>
